--- a/02-tailspin-civic-rev5-ato/artifacts/customer_responsibility_matrix.xlsx
+++ b/02-tailspin-civic-rev5-ato/artifacts/customer_responsibility_matrix.xlsx
@@ -14,11 +14,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Customer Responsibility Matrix'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Customer Responsibility Matrix'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Customer Responsibility Matrix'!$A$1:$I$27</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Summary'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Summary'!$A$1:$D$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Agency Onboarding Checklist'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Agency Onboarding Checklist'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Agency Onboarding Checklist'!$A$1:$G$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Legend'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -162,7 +162,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -252,6 +252,9 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1259,7 +1262,7 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>Notifies US-CERT and the sponsoring agency ISSO within one hour of incident determination; provides incident details and status updates.</t>
+          <t>Notifies CISA and the sponsoring agency ISSO within one hour of incident determination; provides incident details and status updates.</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -1676,7 +1679,7 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col width="24" customWidth="1" style="16" min="1" max="1"/>
+    <col width="30" customWidth="1" style="16" min="1" max="1"/>
     <col width="12" customWidth="1" style="16" min="2" max="2"/>
     <col width="24" customWidth="1" style="16" min="3" max="3"/>
     <col width="60" customWidth="1" style="16" min="4" max="4"/>
@@ -1814,7 +1817,7 @@
     </row>
     <row r="10"/>
     <row r="11" ht="15" customHeight="1" s="17">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>Controls requiring agency action before go-live</t>
         </is>
